--- a/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
@@ -551,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Overview - UI to be updated</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features - This section should move before Source</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Employee Lifecycle</t>
+          <t>Filter Employees</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Lifecycle Configuration</t>
+          <t>Employee Filter Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lifecycle Events</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Event Configuration</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">

--- a/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KW1KV946AH1HVN3SVFCJSDWP</t>
+          <t>h_01KW99M18FJN4C08APNFE610PF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1KV946AH1HVN3SVFCJSDWP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW99M18FJN4C08APNFE610PF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,239 +605,239 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>h_01KW99P5MF7JDAS422WSPRXVMP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW99P5MF7JDAS422WSPRXVMP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Filter Employees</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KW99M18FJN4C08APNFE610PF</t>
+          <t>h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW99M18FJN4C08APNFE610PF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Employee Filter Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KW99P5MF7JDAS422WSPRXVMP</t>
+          <t>h_01KW9CC09AMV3E6K7G5X78EPEV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW99P5MF7JDAS422WSPRXVMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9CC09AMV3E6K7G5X78EPEV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Filter Employees</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
+          <t>h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Employee Filter Configuration</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KW9CC09AMV3E6K7G5X78EPEV</t>
+          <t>h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9CC09AMV3E6K7G5X78EPEV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Service Desk</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
+          <t>h_01KW9D4X0VK01R00G6DA923Z8M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D4X0VK01R00G6DA923Z8M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
+          <t>h_01KW9ND4G30GHT10N3EKKNK6EF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9ND4G30GHT10N3EKKNK6EF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JML Ticket Creation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KW9D4X0VK01R00G6DA923Z8M</t>
+          <t>h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D4X0VK01R00G6DA923Z8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ticket Creation Configuration</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KW9ND4G30GHT10N3EKKNK6EF</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9ND4G30GHT10N3EKKNK6EF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KV580PQB96710J73V3BG96A9</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,41 +869,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,100 +913,100 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Service Desk Bridge</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
     </row>

--- a/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,117 +661,117 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Service Desk</t>
+          <t>Filter Candidates</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
+          <t>h_01KXDDRMW362G65D2D6KHSPNDV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KXDDRMW362G65D2D6KHSPNDV</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Candidate Filter Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
+          <t>h_01KXDDYHXYA3GAYMBVCQJ84037</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KXDDYHXYA3GAYMBVCQJ84037</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JML Ticket Creation</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KW9D4X0VK01R00G6DA923Z8M</t>
+          <t>h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D4X0VK01R00G6DA923Z8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9CSAGF0HRYHGYDKAW8EZT8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ticket Creation Configuration</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KW9ND4G30GHT10N3EKKNK6EF</t>
+          <t>h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9ND4G30GHT10N3EKKNK6EF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D1W0H67X8TBTBZ6JPHRAS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Messaging Application Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KV580PQB96710J73V3BG96A9</t>
+          <t>h_01KY9KWK3VWFFFXW251G14V8WH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KY9KWK3VWFFFXW251G14V8WH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KW9D4X0VK01R00G6DA923Z8M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D4X0VK01R00G6DA923Z8M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,85 +803,85 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KW9ND4G30GHT10N3EKKNK6EF</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9ND4G30GHT10N3EKKNK6EF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,107 +891,107 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KW1KV946AH1HVN3SVFCJSDWP</t>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1KV946AH1HVN3SVFCJSDWP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,54 +1045,120 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Service Desk Bridge</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Jira-Service-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Messaging Application Settings</t>
+          <t>Service Desk Application Configuration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,195 +759,195 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KY9KWK3VWFFFXW251G14V8WH</t>
+          <t>h_01KYVN45H4W8G06FVKZT2P3R5Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KY9KWK3VWFFFXW251G14V8WH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KYVN45H4W8G06FVKZT2P3R5Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JML Ticket Creation</t>
+          <t>Messaging Application Configuration</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KW9D4X0VK01R00G6DA923Z8M</t>
+          <t>h_01KY9KWK3VWFFFXW251G14V8WH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D4X0VK01R00G6DA923Z8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KY9KWK3VWFFFXW251G14V8WH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ticket Creation Configuration</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KW9ND4G30GHT10N3EKKNK6EF</t>
+          <t>h_01KW9D4X0VK01R00G6DA923Z8M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9ND4G30GHT10N3EKKNK6EF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9D4X0VK01R00G6DA923Z8M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KV580PQB96710J73V3BG96A9</t>
+          <t>h_01KW9ND4G30GHT10N3EKKNK6EF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW9ND4G30GHT10N3EKKNK6EF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,129 +979,129 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KW1KV946AH1HVN3SVFCJSDWP</t>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1KV946AH1HVN3SVFCJSDWP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1KV946AH1HVN3SVFCJSDWP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Service Desk Bridge</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,54 +1111,76 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Jira-Service-Management-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
